--- a/Proyecto/Investigadores y Hojas de Vida/Equipo.xlsx
+++ b/Proyecto/Investigadores y Hojas de Vida/Equipo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29103"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unbosqueeduco-my.sharepoint.com/personal/jleongomez_unbosque_edu_co/Documents/Research/Proyecto IDS/Proyecto/Investigadores y Hojas de Vida/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="209" documentId="11_F25DC773A252ABDACC1048AEA11E47925BDE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6CBC80C-3A1F-4AB3-B223-2B169602690B}"/>
+  <xr:revisionPtr revIDLastSave="380" documentId="11_F25DC773A252ABDACC1048AEA11E47925BDE58F6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{783AAA90-1F67-4404-941E-3568B32A9719}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,21 +39,30 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="71">
   <si>
     <t>Nombre</t>
   </si>
   <si>
-    <t>¿Vinculado/a a Universidad El Bosque?</t>
-  </si>
-  <si>
-    <t>Escalafón (olo si tiene vinculación  a UEB)</t>
-  </si>
-  <si>
-    <t>Grupo de Investigación UEB</t>
-  </si>
-  <si>
-    <t>Afiliación</t>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>¿Confirmó interés en participar del proyecto? (escribir "Sí")</t>
+  </si>
+  <si>
+    <t>¿Vinculado/a a Universidad El Bosque? (escribir "Sí" o  "No")</t>
+  </si>
+  <si>
+    <t>Escalafón (solo si tiene vinculación  a UEB)</t>
+  </si>
+  <si>
+    <t>Grupo de Investigación UEB (solo si tiene vinculación  a UEB)</t>
+  </si>
+  <si>
+    <t>Afiliación (puede ser independiente)</t>
+  </si>
+  <si>
+    <t>Horas de dedicación al proyecto (si tiene vinculación  a UEB)</t>
   </si>
   <si>
     <t>Área de experticia</t>
@@ -102,6 +111,12 @@
     <t xml:space="preserve">Juan David Leongómez </t>
   </si>
   <si>
+    <t>jleongomez@unbosque.edu.co</t>
+  </si>
+  <si>
+    <t>Sí</t>
+  </si>
+  <si>
     <t>Profesor Asociado</t>
   </si>
   <si>
@@ -122,6 +137,12 @@
   </si>
   <si>
     <t>Milena Vásquez-Amézquita</t>
+  </si>
+  <si>
+    <t>mvasquezam@unbosque.edu.co</t>
+  </si>
+  <si>
+    <t>Profesor Asociada</t>
   </si>
   <si>
     <t>Neurociencia</t>
@@ -159,7 +180,7 @@
     <t>Nicolás Ignacio Ramos Rodríguez</t>
   </si>
   <si>
-    <t>??</t>
+    <t>ramosnicolas@unbosque.edu.co</t>
   </si>
   <si>
     <t>Investigaciones Pediátricas Bosque</t>
@@ -172,41 +193,46 @@
     <t>Pediatría</t>
   </si>
   <si>
+    <t>Propuestas de posibles aplicaciones clínicas y/o recomendaciones a cuidadores de bebés a partir de resultados. Reclutamiento de participantes.</t>
+  </si>
+  <si>
     <t>María Catalina Bagés Mesa</t>
   </si>
   <si>
+    <t>bagesmaria@unbosque.edu.co</t>
+  </si>
+  <si>
     <t>Bertha Patricia Calderón Ortiz</t>
   </si>
   <si>
+    <t>bercalde@unbosque.edu.co</t>
+  </si>
+  <si>
     <t>Jimena Varela Perez</t>
   </si>
   <si>
+    <t>??</t>
+  </si>
+  <si>
     <t>Daniel Toro Avila</t>
   </si>
   <si>
+    <t>dtoroavila@gmail.com</t>
+  </si>
+  <si>
     <t>Adriana María Cristancho Arévalo</t>
   </si>
   <si>
+    <t>adrianacristancho81@gmail.com</t>
+  </si>
+  <si>
     <t>Lia Sanmiguel Ardila</t>
   </si>
   <si>
-    <t>Ana María Ángel Sanin</t>
-  </si>
-  <si>
-    <t>Diseño imagen y comunicación</t>
-  </si>
-  <si>
-    <t>Facultad de Creación y Comunicación
-Universidad El Bosque</t>
-  </si>
-  <si>
-    <t>Diseño y comunicación</t>
-  </si>
-  <si>
-    <t>Diana Obregón</t>
-  </si>
-  <si>
-    <t>Por definir</t>
+    <t xml:space="preserve"> Ruth Stella Chacon Pinilla</t>
+  </si>
+  <si>
+    <t>chaconruth@unbosque.edu.co</t>
   </si>
   <si>
     <t>Educación e Investigación UNBOSQUE</t>
@@ -219,13 +245,40 @@
     <t>Educación</t>
   </si>
   <si>
+    <t>Lina Maria Rodríguez Granada</t>
+  </si>
+  <si>
+    <t>rodriguezlina@unbosque.edu.co</t>
+  </si>
+  <si>
+    <t>Psicología de la salud, del deporte y clínica</t>
+  </si>
+  <si>
+    <t>Música</t>
+  </si>
+  <si>
+    <t>Luz Helena Buitrago León</t>
+  </si>
+  <si>
+    <t>buitragoluz@unbosque.edu.co</t>
+  </si>
+  <si>
+    <t>Profesora Titular</t>
+  </si>
+  <si>
+    <t>Psicología del desarrollo</t>
+  </si>
+  <si>
     <t>Natalia Moreno-Buitrago</t>
   </si>
   <si>
+    <t>morenobuitrago.1@buckeyemail.osu.edu</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
     <t>NA</t>
-  </si>
-  <si>
-    <t>Externo</t>
   </si>
   <si>
     <t>Candidata Doctoral
@@ -244,6 +297,9 @@
   </si>
   <si>
     <t>David A. Puts</t>
+  </si>
+  <si>
+    <t>dap27@psu.edu</t>
   </si>
   <si>
     <t>Profesor Titular
@@ -355,7 +411,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -370,19 +426,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFD7D7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF8DB3E2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6E3BC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -394,7 +438,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,30 +497,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -504,7 +548,22 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -512,21 +571,34 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
+  <dxfs count="20">
     <dxf>
       <font>
         <strike val="0"/>
@@ -695,6 +767,41 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="8"/>
+        <color rgb="FF000000"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -837,6 +944,93 @@
           <xfpb:DXFComplement i="0"/>
         </ext>
       </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{0417FA29-78FA-4A13-93AC-8FF0FAFDF519}">
+          <xfpb:DXFComplement i="0"/>
+        </ext>
+      </extLst>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color theme="10"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -931,6 +1125,46 @@
         <bottom/>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -979,26 +1213,29 @@
 <file path=xl/namedSheetViews/namedSheetView1.xml><?xml version="1.0" encoding="utf-8"?>
 <namedSheetViews xmlns="http://schemas.microsoft.com/office/spreadsheetml/2019/namedsheetviews" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <namedSheetView name="View1" id="{BFBF76A3-6B92-422A-A127-E7C554C462B6}">
-    <nsvFilter filterId="{47312F7A-547A-4F0B-93CB-2465DECF0052}" ref="A1:I15" tableId="2"/>
+    <nsvFilter filterId="{47312F7A-547A-4F0B-93CB-2465DECF0052}" ref="A1:L15" tableId="2"/>
   </namedSheetView>
 </namedSheetViews>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47312F7A-547A-4F0B-93CB-2465DECF0052}" name="Table2" displayName="Table2" ref="A1:I15" totalsRowShown="0" headerRowDxfId="12" dataDxfId="11" headerRowBorderDxfId="9" tableBorderDxfId="10">
-  <autoFilter ref="A1:I15" xr:uid="{47312F7A-547A-4F0B-93CB-2465DECF0052}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{CBE926E6-CA94-4D1D-8861-D88C4BDF8319}" name="Nombre" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{9FF25A8F-1632-449B-B0EA-64A42CE0FCC9}" name="¿Vinculado/a a Universidad El Bosque?" dataDxfId="7" dataCellStyle="Hyperlink"/>
-    <tableColumn id="9" xr3:uid="{9932D20C-4607-4B9E-A778-17B02C4DD9A8}" name="Escalafón (olo si tiene vinculación  a UEB)" dataDxfId="6" dataCellStyle="Hyperlink"/>
-    <tableColumn id="2" xr3:uid="{97992357-7905-421E-8442-3A19646EED47}" name="Grupo de Investigación UEB" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{7CCDB552-A2C4-47E1-A2DD-E278BE5EE7A3}" name="Afiliación" dataDxfId="4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{47312F7A-547A-4F0B-93CB-2465DECF0052}" name="Table2" displayName="Table2" ref="A1:L15" totalsRowShown="0" headerRowDxfId="15" dataDxfId="14" headerRowBorderDxfId="12" tableBorderDxfId="13">
+  <autoFilter ref="A1:L15" xr:uid="{47312F7A-547A-4F0B-93CB-2465DECF0052}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{CBE926E6-CA94-4D1D-8861-D88C4BDF8319}" name="Nombre" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{91955337-FCBC-4858-A4F9-C86C8526264F}" name="Email" dataDxfId="10" dataCellStyle="Hyperlink"/>
+    <tableColumn id="10" xr3:uid="{39674408-044E-4FA3-B1D4-8D8288B7E01A}" name="¿Confirmó interés en participar del proyecto? (escribir &quot;Sí&quot;)" dataDxfId="9" dataCellStyle="Hyperlink"/>
+    <tableColumn id="7" xr3:uid="{9FF25A8F-1632-449B-B0EA-64A42CE0FCC9}" name="¿Vinculado/a a Universidad El Bosque? (escribir &quot;Sí&quot; o  &quot;No&quot;)" dataDxfId="8" dataCellStyle="Hyperlink"/>
+    <tableColumn id="9" xr3:uid="{9932D20C-4607-4B9E-A778-17B02C4DD9A8}" name="Escalafón (solo si tiene vinculación  a UEB)" dataDxfId="7" dataCellStyle="Hyperlink"/>
+    <tableColumn id="2" xr3:uid="{97992357-7905-421E-8442-3A19646EED47}" name="Grupo de Investigación UEB (solo si tiene vinculación  a UEB)" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{7CCDB552-A2C4-47E1-A2DD-E278BE5EE7A3}" name="Afiliación (puede ser independiente)" dataDxfId="5"/>
+    <tableColumn id="11" xr3:uid="{A7FD3D32-CE28-452E-B65F-D97A18133D23}" name="Horas de dedicación al proyecto (si tiene vinculación  a UEB)" dataDxfId="4"/>
     <tableColumn id="4" xr3:uid="{9EF7D58A-EFEE-418D-9857-812A63D5E535}" name="Área de experticia" dataDxfId="3"/>
     <tableColumn id="6" xr3:uid="{EBB00359-FA2C-4391-AD36-06CDDC098B78}" name="Hoja de Vida_x000a_(agregar PDF a esta carpeta)" dataDxfId="2"/>
     <tableColumn id="8" xr3:uid="{18C0D0E2-C0F1-42CA-ADA2-1520B313B6CA}" name="Experticia y formación relevantes" dataDxfId="1"/>
     <tableColumn id="5" xr3:uid="{324113BD-A453-4F36-ABA5-0E1DCC66FDFC}" name="Funciones en el proyecto" dataDxfId="0"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -1265,408 +1502,524 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:L16"/>
   <sheetFormatPr defaultColWidth="19.42578125" defaultRowHeight="15"/>
   <cols>
-    <col min="5" max="5" width="25.42578125" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.5703125" customWidth="1"/>
+    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="7" max="7" width="19.140625" customWidth="1"/>
+    <col min="8" max="8" width="18.140625" customWidth="1"/>
+    <col min="9" max="9" width="14.28515625" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" customWidth="1"/>
+    <col min="11" max="11" width="29.85546875" customWidth="1"/>
+    <col min="12" max="12" width="33.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="37.5">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:12" ht="37.5">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="69.75">
-      <c r="A2" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="15" t="b">
+    <row r="2" spans="1:12" ht="46.5">
+      <c r="A2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="22">
+        <v>12</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="10" t="b">
+      <c r="K2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="36">
+      <c r="A3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="F3" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="22">
+        <v>4</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="J3" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="K3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="34.5">
+      <c r="A4" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>15</v>
+      <c r="D4" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="15"/>
+      <c r="F4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="15"/>
+      <c r="I4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="60">
-      <c r="A3" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="15" t="b">
+    <row r="5" spans="1:12" ht="34.5">
+      <c r="A5" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="15"/>
+      <c r="F5" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H5" s="15"/>
+      <c r="I5" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="C3" s="18" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="K5" s="4"/>
+      <c r="L5" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="34.5">
+      <c r="A6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="34.5">
+      <c r="A7" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="15"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="34.5">
+      <c r="A8" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="15"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J8" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="34.5">
+      <c r="A9" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E9" s="15"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J9" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="34.5">
+      <c r="A10" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="15"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="23.25">
+      <c r="A11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E11" s="15"/>
+      <c r="F11" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="15"/>
+      <c r="I11" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
+    </row>
+    <row r="12" spans="1:12" ht="23.25">
+      <c r="A12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="15"/>
+      <c r="F12" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="10" t="b">
+      <c r="H12" s="15"/>
+      <c r="I12" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="J12" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K12" s="4"/>
+      <c r="L12" s="20"/>
+    </row>
+    <row r="13" spans="1:12" ht="23.25">
+      <c r="A13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="15"/>
+      <c r="I13" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="J13" s="19" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" s="4"/>
+      <c r="L13" s="20"/>
+    </row>
+    <row r="14" spans="1:12" ht="46.5">
+      <c r="A14" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="L14" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="58.5" customHeight="1">
+      <c r="A15" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="H15" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="J15" s="8" t="b">
         <v>1</v>
       </c>
-      <c r="H3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>19</v>
+      <c r="K15" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L15" s="4" t="s">
+        <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="23.25">
-      <c r="A4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:9" ht="23.25">
-      <c r="A5" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9" ht="23.25">
-      <c r="A6" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B6" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="B7" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5"/>
-    </row>
-    <row r="9" spans="1:9" ht="23.25">
-      <c r="A9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B10" s="16" t="b">
-        <v>0</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="1:9" ht="23.25">
-      <c r="A11" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="B11" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G11" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-    </row>
-    <row r="12" spans="1:9" ht="23.25">
-      <c r="A12" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G12" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5"/>
-    </row>
-    <row r="13" spans="1:9" ht="23.25">
-      <c r="A13" s="17" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="16" t="b">
-        <v>1</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G13" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-    </row>
-    <row r="14" spans="1:9" ht="69.75">
-      <c r="A14" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="10" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="92.25">
-      <c r="A15" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="B15" s="15" t="b">
-        <v>0</v>
-      </c>
-      <c r="C15" s="18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="G15" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I15" s="5" t="s">
-        <v>51</v>
-      </c>
+    <row r="16" spans="1:12">
+      <c r="B16" s="24"/>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B2:L15">
+    <cfRule type="containsBlanks" dxfId="19" priority="4">
+      <formula>LEN(TRIM(B2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:D15">
+    <cfRule type="cellIs" dxfId="18" priority="3" operator="equal">
+      <formula>"Sí"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C2:D15">
+    <cfRule type="containsText" dxfId="17" priority="2" operator="containsText" text="Si">
+      <formula>NOT(ISERROR(SEARCH("Si",C2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D15">
+    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",D2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" tooltip="https://jdleongomez.info/es/" display="https://jdleongomez.info/es/" xr:uid="{3A33ABB0-73AF-4D0F-BDCA-A069AD9C672B}"/>
     <hyperlink ref="A3" r:id="rId2" tooltip="https://scholar.google.es/citations?user=XgNEpfgAAAAJ" display="https://scholar.google.es/citations?user=XgNEpfgAAAAJ" xr:uid="{EC50744A-AD64-4DCC-9872-F656AAABC5B7}"/>
@@ -1676,16 +2029,29 @@
     <hyperlink ref="A7" r:id="rId6" tooltip="https://www.linkedin.com/in/jimena-varela-pediatra/?originalSubdomain=co" display="https://www.linkedin.com/in/jimena-varela-pediatra/?originalSubdomain=co" xr:uid="{074AF766-1841-4C84-BE85-447609ED2808}"/>
     <hyperlink ref="A8" r:id="rId7" tooltip="https://www.linkedin.com/in/danieltoroavilapediatra/?originalSubdomain=co" display="https://www.linkedin.com/in/danieltoroavilapediatra/?originalSubdomain=co" xr:uid="{4B8AEC4D-87D9-44E1-A198-D8BF47792282}"/>
     <hyperlink ref="A9" r:id="rId8" tooltip="https://www.linkedin.com/in/adriana-mar%C3%ADa-cristancho-ar%C3%A9valo-aa670354/?originalSubdomain=co" display="https://www.linkedin.com/in/adriana-mar%C3%ADa-cristancho-ar%C3%A9valo-aa670354/?originalSubdomain=co" xr:uid="{137DC6E1-A6D7-4299-8288-A3B2C71289DC}"/>
-    <hyperlink ref="A11" r:id="rId9" tooltip="https://scienti.minciencias.gov.co/cvlac/visualizador/generarCurriculoCv.do?cod_rh=0001632284" display="https://scienti.minciencias.gov.co/cvlac/visualizador/generarCurriculoCv.do?cod_rh=0001632284" xr:uid="{98656D16-C753-4E1A-9C6E-6F9654580454}"/>
-    <hyperlink ref="A12" r:id="rId10" tooltip="https://www.researchgate.net/profile/Diana-Obregon-6" display="https://www.researchgate.net/profile/Diana-Obregon-6" xr:uid="{7EEDB962-597B-42CB-97ED-7D4380577EF6}"/>
-    <hyperlink ref="A14" r:id="rId11" tooltip="https://music.osu.edu/people/morenobuitrago.1" display="https://music.osu.edu/people/morenobuitrago.1" xr:uid="{302796FD-8283-4AED-9016-9B5129B4B1A6}"/>
-    <hyperlink ref="A15" r:id="rId12" tooltip="https://beel.la.psu.edu/labstaff/" display="https://beel.la.psu.edu/labstaff/" xr:uid="{AB215533-3ECF-45BB-BD5B-2356FF2CC1B4}"/>
-    <hyperlink ref="G1" r:id="rId13" display="../../../../../../../:f:/g/personal/jleongomez_unbosque_edu_co/EvkI-nvgfplAo6If15j514wBMNKexevxx3wLN_5Ao4Ck1Q?e=M4Exdy" xr:uid="{DC05F3E5-07C0-4732-883C-6E51783348A4}"/>
+    <hyperlink ref="A14" r:id="rId9" tooltip="https://music.osu.edu/people/morenobuitrago.1" display="https://music.osu.edu/people/morenobuitrago.1" xr:uid="{302796FD-8283-4AED-9016-9B5129B4B1A6}"/>
+    <hyperlink ref="A15" r:id="rId10" tooltip="https://beel.la.psu.edu/labstaff/" display="https://beel.la.psu.edu/labstaff/" xr:uid="{AB215533-3ECF-45BB-BD5B-2356FF2CC1B4}"/>
+    <hyperlink ref="J1" r:id="rId11" display="../../../../../../../:f:/g/personal/jleongomez_unbosque_edu_co/EvkI-nvgfplAo6If15j514wBMNKexevxx3wLN_5Ao4Ck1Q?e=M4Exdy" xr:uid="{DC05F3E5-07C0-4732-883C-6E51783348A4}"/>
+    <hyperlink ref="A11" r:id="rId12" xr:uid="{6922178B-2905-4997-80A4-7515C6571B23}"/>
+    <hyperlink ref="A13" r:id="rId13" xr:uid="{86F05EE1-1846-4841-9E77-52EC6471F97A}"/>
+    <hyperlink ref="A12" r:id="rId14" xr:uid="{2B4474F8-D023-4A5D-8CE4-DB24E1C0C9FC}"/>
+    <hyperlink ref="B2" r:id="rId15" xr:uid="{E21A6ACE-BFCC-4AE9-81D5-965FA4E444D0}"/>
+    <hyperlink ref="B3" r:id="rId16" xr:uid="{97691FF5-530A-41CC-97B1-7952EAA8D250}"/>
+    <hyperlink ref="B4" r:id="rId17" xr:uid="{6C66C659-144F-4F57-BC85-F73E43581BEE}"/>
+    <hyperlink ref="B5" r:id="rId18" xr:uid="{7C5EC24C-25B7-44E8-A659-A0A4CEB0E827}"/>
+    <hyperlink ref="B6" r:id="rId19" xr:uid="{24674C4D-6C39-4271-9299-583A5AFF1538}"/>
+    <hyperlink ref="B8" r:id="rId20" xr:uid="{B9C32B0E-917A-463E-A3DE-024359807BB6}"/>
+    <hyperlink ref="B9" r:id="rId21" xr:uid="{84848C11-3195-471F-A7B4-4A3A1FBDF469}"/>
+    <hyperlink ref="B11" r:id="rId22" xr:uid="{CECB5071-134B-42F0-B8D1-E61BFA44E767}"/>
+    <hyperlink ref="B12" r:id="rId23" xr:uid="{3A574D94-D7CA-4451-A1E8-A047607245A6}"/>
+    <hyperlink ref="B13" r:id="rId24" xr:uid="{E961C4A0-6C01-4E84-9EA5-C9B102A6EDAE}"/>
+    <hyperlink ref="B14" r:id="rId25" xr:uid="{D3C049AF-5C87-4679-99E3-E4F0BFD74BF2}"/>
+    <hyperlink ref="B15" r:id="rId26" xr:uid="{483E38E9-A7F6-4299-A0FA-A2033F198F8D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="43" orientation="portrait" r:id="rId14"/>
+  <pageSetup scale="43" orientation="portrait" r:id="rId27"/>
   <tableParts count="1">
-    <tablePart r:id="rId15"/>
+    <tablePart r:id="rId28"/>
   </tableParts>
 </worksheet>
 </file>